--- a/data/availability/projects/madinet-masr/elm-tree-park.xlsx
+++ b/data/availability/projects/madinet-masr/elm-tree-park.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S-Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -809,7 +809,6 @@
       <c r="G2" t="n">
         <v>212</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -866,7 +865,6 @@
       <c r="G3" t="n">
         <v>180</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -923,7 +921,6 @@
       <c r="G4" t="n">
         <v>175</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
